--- a/artfynd/A 25176-2025 artfynd.xlsx
+++ b/artfynd/A 25176-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132821244</v>
+        <v>132821234</v>
       </c>
       <c r="B2" t="n">
-        <v>83182</v>
+        <v>83222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566946</v>
+        <v>567009</v>
       </c>
       <c r="R2" t="n">
-        <v>7220767</v>
+        <v>7220842</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132821243</v>
+        <v>132821244</v>
       </c>
       <c r="B3" t="n">
-        <v>79334</v>
+        <v>83222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566953</v>
+        <v>566946</v>
       </c>
       <c r="R3" t="n">
-        <v>7220770</v>
+        <v>7220767</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,14 +889,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132821241</v>
+        <v>132821235</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567031</v>
+        <v>567010</v>
       </c>
       <c r="R4" t="n">
-        <v>7220791</v>
+        <v>7220848</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,50 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132821236</v>
+        <v>132821240</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nymyran, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567033</v>
+        <v>567058</v>
       </c>
       <c r="R5" t="n">
-        <v>7220841</v>
+        <v>7220811</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132821245</v>
+        <v>132821241</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566946</v>
+        <v>567031</v>
       </c>
       <c r="R6" t="n">
-        <v>7220767</v>
+        <v>7220791</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132821235</v>
+        <v>132821243</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567010</v>
+        <v>566953</v>
       </c>
       <c r="R7" t="n">
-        <v>7220848</v>
+        <v>7220770</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,14 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132821248</v>
+        <v>132821245</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566788</v>
+        <v>566946</v>
       </c>
       <c r="R8" t="n">
-        <v>7220798</v>
+        <v>7220767</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132821239</v>
+        <v>132821246</v>
       </c>
       <c r="B9" t="n">
-        <v>97997</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567057</v>
+        <v>566929</v>
       </c>
       <c r="R9" t="n">
-        <v>7220819</v>
+        <v>7220758</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1499,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132821234</v>
+        <v>132821248</v>
       </c>
       <c r="B10" t="n">
-        <v>83182</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567009</v>
+        <v>566788</v>
       </c>
       <c r="R10" t="n">
-        <v>7220842</v>
+        <v>7220798</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1606,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132821246</v>
+        <v>132821236</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,34 +1649,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nymyran, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566929</v>
+        <v>567033</v>
       </c>
       <c r="R11" t="n">
-        <v>7220758</v>
+        <v>7220841</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132821240</v>
+        <v>132821238</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,34 +1761,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nymyran, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567058</v>
+        <v>567059</v>
       </c>
       <c r="R12" t="n">
-        <v>7220811</v>
+        <v>7220817</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1860,7 +1865,7 @@
         <v>132821242</v>
       </c>
       <c r="B13" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132821238</v>
+        <v>132821247</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2005,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2009,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567059</v>
+        <v>566830</v>
       </c>
       <c r="R14" t="n">
-        <v>7220817</v>
+        <v>7220787</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2044,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2078,6 +2083,113 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132821239</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nymyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>567057</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7220819</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>05:55</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>05:55</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
